--- a/data/raw/companies.xlsx
+++ b/data/raw/companies.xlsx
@@ -1946,16 +1946,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1978,7 +1970,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1986,35 +1978,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2314,34 +2288,34 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2370,7 +2344,7 @@
       <c r="H2">
         <v>513344.3</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>458</v>
       </c>
       <c r="J2" t="s">
@@ -2402,7 +2376,7 @@
       <c r="H3">
         <v>182452.54</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>459</v>
       </c>
       <c r="J3" t="s">
@@ -2434,7 +2408,7 @@
       <c r="H4">
         <v>593830.86</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>460</v>
       </c>
       <c r="J4" t="s">
@@ -2466,7 +2440,7 @@
       <c r="H5">
         <v>340427.85</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="1" t="s">
         <v>461</v>
       </c>
       <c r="J5" t="s">
@@ -2498,7 +2472,7 @@
       <c r="H6">
         <v>189965.41</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="1" t="s">
         <v>462</v>
       </c>
       <c r="J6" t="s">
@@ -2530,7 +2504,7 @@
       <c r="H7">
         <v>163075.93</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="1" t="s">
         <v>463</v>
       </c>
       <c r="J7" t="s">
@@ -2562,7 +2536,7 @@
       <c r="H8">
         <v>362121.19</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="1" t="s">
         <v>464</v>
       </c>
       <c r="J8" t="s">
@@ -2594,7 +2568,7 @@
       <c r="H9">
         <v>645626.3100000001</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="1" t="s">
         <v>465</v>
       </c>
       <c r="J9" t="s">
@@ -2626,7 +2600,7 @@
       <c r="H10">
         <v>225907.72</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="1" t="s">
         <v>466</v>
       </c>
       <c r="J10" t="s">
@@ -2658,7 +2632,7 @@
       <c r="H11">
         <v>78732.95</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="1" t="s">
         <v>467</v>
       </c>
       <c r="J11" t="s">
@@ -2690,7 +2664,7 @@
       <c r="H12">
         <v>484962.19</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="1" t="s">
         <v>468</v>
       </c>
       <c r="J12" t="s">
@@ -2722,7 +2696,7 @@
       <c r="H13">
         <v>104236.8</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="1" t="s">
         <v>469</v>
       </c>
       <c r="J13" t="s">
@@ -2754,7 +2728,7 @@
       <c r="H14">
         <v>238076.73</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="1" t="s">
         <v>470</v>
       </c>
       <c r="J14" t="s">
@@ -2786,7 +2760,7 @@
       <c r="H15">
         <v>157869.43</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="1" t="s">
         <v>471</v>
       </c>
       <c r="J15" t="s">
@@ -2818,7 +2792,7 @@
       <c r="H16">
         <v>186179.13</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="1" t="s">
         <v>472</v>
       </c>
       <c r="J16" t="s">
@@ -2850,7 +2824,7 @@
       <c r="H17">
         <v>693854.52</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="1" t="s">
         <v>473</v>
       </c>
       <c r="J17" t="s">
@@ -2882,7 +2856,7 @@
       <c r="H18">
         <v>510369.13</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="1" t="s">
         <v>474</v>
       </c>
       <c r="J18" t="s">
@@ -2914,7 +2888,7 @@
       <c r="H19">
         <v>287440.21</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="1" t="s">
         <v>475</v>
       </c>
       <c r="J19" t="s">
@@ -2946,7 +2920,7 @@
       <c r="H20">
         <v>749640.4</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="I20" s="1" t="s">
         <v>476</v>
       </c>
       <c r="J20" t="s">
@@ -2978,7 +2952,7 @@
       <c r="H21">
         <v>509807.74</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="I21" s="1" t="s">
         <v>477</v>
       </c>
       <c r="J21" t="s">
@@ -3010,7 +2984,7 @@
       <c r="H22">
         <v>372496.87</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="I22" s="1" t="s">
         <v>478</v>
       </c>
       <c r="J22" t="s">
@@ -3042,7 +3016,7 @@
       <c r="H23">
         <v>262804.77</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="I23" s="1" t="s">
         <v>479</v>
       </c>
       <c r="J23" t="s">
@@ -3074,7 +3048,7 @@
       <c r="H24">
         <v>645011.41</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="I24" s="1" t="s">
         <v>480</v>
       </c>
       <c r="J24" t="s">
@@ -3106,7 +3080,7 @@
       <c r="H25">
         <v>172731.36</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="1" t="s">
         <v>481</v>
       </c>
       <c r="J25" t="s">
@@ -3138,7 +3112,7 @@
       <c r="H26">
         <v>526073.74</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="I26" s="1" t="s">
         <v>482</v>
       </c>
       <c r="J26" t="s">
@@ -3170,7 +3144,7 @@
       <c r="H27">
         <v>215579.73</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="I27" s="1" t="s">
         <v>483</v>
       </c>
       <c r="J27" t="s">
@@ -3202,7 +3176,7 @@
       <c r="H28">
         <v>469745.86</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="I28" s="1" t="s">
         <v>484</v>
       </c>
       <c r="J28" t="s">
@@ -3234,7 +3208,7 @@
       <c r="H29">
         <v>179360</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="I29" s="1" t="s">
         <v>485</v>
       </c>
       <c r="J29" t="s">
@@ -3266,7 +3240,7 @@
       <c r="H30">
         <v>605846.8199999999</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="I30" s="1" t="s">
         <v>486</v>
       </c>
       <c r="J30" t="s">
@@ -3298,7 +3272,7 @@
       <c r="H31">
         <v>132185.69</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="I31" s="1" t="s">
         <v>487</v>
       </c>
       <c r="J31" t="s">
@@ -3330,7 +3304,7 @@
       <c r="H32">
         <v>55504.53</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="I32" s="1" t="s">
         <v>488</v>
       </c>
       <c r="J32" t="s">
@@ -3362,7 +3336,7 @@
       <c r="H33">
         <v>204874.23</v>
       </c>
-      <c r="I33" s="2" t="s">
+      <c r="I33" s="1" t="s">
         <v>489</v>
       </c>
       <c r="J33" t="s">
@@ -3394,7 +3368,7 @@
       <c r="H34">
         <v>577973.85</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="I34" s="1" t="s">
         <v>490</v>
       </c>
       <c r="J34" t="s">
@@ -3426,7 +3400,7 @@
       <c r="H35">
         <v>514564.63</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="I35" s="1" t="s">
         <v>491</v>
       </c>
       <c r="J35" t="s">
@@ -3458,7 +3432,7 @@
       <c r="H36">
         <v>130735.41</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="I36" s="1" t="s">
         <v>492</v>
       </c>
       <c r="J36" t="s">
@@ -3490,7 +3464,7 @@
       <c r="H37">
         <v>610759.95</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="I37" s="1" t="s">
         <v>493</v>
       </c>
       <c r="J37" t="s">
@@ -3522,7 +3496,7 @@
       <c r="H38">
         <v>242263.61</v>
       </c>
-      <c r="I38" s="2" t="s">
+      <c r="I38" s="1" t="s">
         <v>494</v>
       </c>
       <c r="J38" t="s">
@@ -3554,7 +3528,7 @@
       <c r="H39">
         <v>302261.51</v>
       </c>
-      <c r="I39" s="2" t="s">
+      <c r="I39" s="1" t="s">
         <v>495</v>
       </c>
       <c r="J39" t="s">
@@ -3586,7 +3560,7 @@
       <c r="H40">
         <v>262704.07</v>
       </c>
-      <c r="I40" s="2" t="s">
+      <c r="I40" s="1" t="s">
         <v>496</v>
       </c>
       <c r="J40" t="s">
@@ -3618,7 +3592,7 @@
       <c r="H41">
         <v>703583.89</v>
       </c>
-      <c r="I41" s="2" t="s">
+      <c r="I41" s="1" t="s">
         <v>497</v>
       </c>
       <c r="J41" t="s">
@@ -3650,7 +3624,7 @@
       <c r="H42">
         <v>196492.92</v>
       </c>
-      <c r="I42" s="2" t="s">
+      <c r="I42" s="1" t="s">
         <v>498</v>
       </c>
       <c r="J42" t="s">
@@ -3682,7 +3656,7 @@
       <c r="H43">
         <v>586866.54</v>
       </c>
-      <c r="I43" s="2" t="s">
+      <c r="I43" s="1" t="s">
         <v>499</v>
       </c>
       <c r="J43" t="s">
@@ -3714,7 +3688,7 @@
       <c r="H44">
         <v>529501.9</v>
       </c>
-      <c r="I44" s="2" t="s">
+      <c r="I44" s="1" t="s">
         <v>500</v>
       </c>
       <c r="J44" t="s">
@@ -3746,7 +3720,7 @@
       <c r="H45">
         <v>424500.66</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="I45" s="1" t="s">
         <v>501</v>
       </c>
       <c r="J45" t="s">
@@ -3778,7 +3752,7 @@
       <c r="H46">
         <v>743486.23</v>
       </c>
-      <c r="I46" s="2" t="s">
+      <c r="I46" s="1" t="s">
         <v>502</v>
       </c>
       <c r="J46" t="s">
@@ -3810,7 +3784,7 @@
       <c r="H47">
         <v>252814.45</v>
       </c>
-      <c r="I47" s="2" t="s">
+      <c r="I47" s="1" t="s">
         <v>503</v>
       </c>
       <c r="J47" t="s">
@@ -3842,7 +3816,7 @@
       <c r="H48">
         <v>720193.2</v>
       </c>
-      <c r="I48" s="2" t="s">
+      <c r="I48" s="1" t="s">
         <v>504</v>
       </c>
       <c r="J48" t="s">
@@ -3874,7 +3848,7 @@
       <c r="H49">
         <v>183634.38</v>
       </c>
-      <c r="I49" s="2" t="s">
+      <c r="I49" s="1" t="s">
         <v>505</v>
       </c>
       <c r="J49" t="s">
@@ -3906,7 +3880,7 @@
       <c r="H50">
         <v>445367.61</v>
       </c>
-      <c r="I50" s="2" t="s">
+      <c r="I50" s="1" t="s">
         <v>506</v>
       </c>
       <c r="J50" t="s">
@@ -3938,7 +3912,7 @@
       <c r="H51">
         <v>61439.5</v>
       </c>
-      <c r="I51" s="2" t="s">
+      <c r="I51" s="1" t="s">
         <v>507</v>
       </c>
       <c r="J51" t="s">
@@ -3970,7 +3944,7 @@
       <c r="H52">
         <v>58583.26</v>
       </c>
-      <c r="I52" s="2" t="s">
+      <c r="I52" s="1" t="s">
         <v>508</v>
       </c>
       <c r="J52" t="s">
@@ -4002,7 +3976,7 @@
       <c r="H53">
         <v>413754.12</v>
       </c>
-      <c r="I53" s="2" t="s">
+      <c r="I53" s="1" t="s">
         <v>509</v>
       </c>
       <c r="J53" t="s">
@@ -4034,7 +4008,7 @@
       <c r="H54">
         <v>433690.98</v>
       </c>
-      <c r="I54" s="2" t="s">
+      <c r="I54" s="1" t="s">
         <v>510</v>
       </c>
       <c r="J54" t="s">
@@ -4066,7 +4040,7 @@
       <c r="H55">
         <v>628772.4399999999</v>
       </c>
-      <c r="I55" s="2" t="s">
+      <c r="I55" s="1" t="s">
         <v>511</v>
       </c>
       <c r="J55" t="s">
@@ -4098,7 +4072,7 @@
       <c r="H56">
         <v>82060</v>
       </c>
-      <c r="I56" s="2" t="s">
+      <c r="I56" s="1" t="s">
         <v>512</v>
       </c>
       <c r="J56" t="s">
@@ -4130,7 +4104,7 @@
       <c r="H57">
         <v>331826.31</v>
       </c>
-      <c r="I57" s="2" t="s">
+      <c r="I57" s="1" t="s">
         <v>513</v>
       </c>
       <c r="J57" t="s">
@@ -4162,7 +4136,7 @@
       <c r="H58">
         <v>524497.11</v>
       </c>
-      <c r="I58" s="2" t="s">
+      <c r="I58" s="1" t="s">
         <v>514</v>
       </c>
       <c r="J58" t="s">
@@ -4194,7 +4168,7 @@
       <c r="H59">
         <v>325083.92</v>
       </c>
-      <c r="I59" s="2" t="s">
+      <c r="I59" s="1" t="s">
         <v>515</v>
       </c>
       <c r="J59" t="s">
@@ -4226,7 +4200,7 @@
       <c r="H60">
         <v>157314.11</v>
       </c>
-      <c r="I60" s="2" t="s">
+      <c r="I60" s="1" t="s">
         <v>516</v>
       </c>
       <c r="J60" t="s">
@@ -4258,7 +4232,7 @@
       <c r="H61">
         <v>340395.9</v>
       </c>
-      <c r="I61" s="2" t="s">
+      <c r="I61" s="1" t="s">
         <v>517</v>
       </c>
       <c r="J61" t="s">
@@ -4290,7 +4264,7 @@
       <c r="H62">
         <v>700216.33</v>
       </c>
-      <c r="I62" s="2" t="s">
+      <c r="I62" s="1" t="s">
         <v>518</v>
       </c>
       <c r="J62" t="s">
@@ -4322,7 +4296,7 @@
       <c r="H63">
         <v>689772.54</v>
       </c>
-      <c r="I63" s="2" t="s">
+      <c r="I63" s="1" t="s">
         <v>519</v>
       </c>
       <c r="J63" t="s">
@@ -4354,7 +4328,7 @@
       <c r="H64">
         <v>523455.19</v>
       </c>
-      <c r="I64" s="2" t="s">
+      <c r="I64" s="1" t="s">
         <v>520</v>
       </c>
       <c r="J64" t="s">
@@ -4386,7 +4360,7 @@
       <c r="H65">
         <v>741461.75</v>
       </c>
-      <c r="I65" s="2" t="s">
+      <c r="I65" s="1" t="s">
         <v>521</v>
       </c>
       <c r="J65" t="s">
@@ -4418,7 +4392,7 @@
       <c r="H66">
         <v>391084.69</v>
       </c>
-      <c r="I66" s="2" t="s">
+      <c r="I66" s="1" t="s">
         <v>522</v>
       </c>
       <c r="J66" t="s">
@@ -4450,7 +4424,7 @@
       <c r="H67">
         <v>135886.51</v>
       </c>
-      <c r="I67" s="2" t="s">
+      <c r="I67" s="1" t="s">
         <v>523</v>
       </c>
       <c r="J67" t="s">
@@ -4482,7 +4456,7 @@
       <c r="H68">
         <v>741581.87</v>
       </c>
-      <c r="I68" s="2" t="s">
+      <c r="I68" s="1" t="s">
         <v>524</v>
       </c>
       <c r="J68" t="s">
@@ -4514,7 +4488,7 @@
       <c r="H69">
         <v>558790.25</v>
       </c>
-      <c r="I69" s="2" t="s">
+      <c r="I69" s="1" t="s">
         <v>525</v>
       </c>
       <c r="J69" t="s">
@@ -4546,7 +4520,7 @@
       <c r="H70">
         <v>155968.8</v>
       </c>
-      <c r="I70" s="2" t="s">
+      <c r="I70" s="1" t="s">
         <v>526</v>
       </c>
       <c r="J70" t="s">
@@ -4578,7 +4552,7 @@
       <c r="H71">
         <v>589911.0600000001</v>
       </c>
-      <c r="I71" s="2" t="s">
+      <c r="I71" s="1" t="s">
         <v>527</v>
       </c>
       <c r="J71" t="s">
@@ -4610,7 +4584,7 @@
       <c r="H72">
         <v>44863.16</v>
       </c>
-      <c r="I72" s="2" t="s">
+      <c r="I72" s="1" t="s">
         <v>528</v>
       </c>
       <c r="J72" t="s">
@@ -4642,7 +4616,7 @@
       <c r="H73">
         <v>768819.23</v>
       </c>
-      <c r="I73" s="2" t="s">
+      <c r="I73" s="1" t="s">
         <v>529</v>
       </c>
       <c r="J73" t="s">
@@ -4674,7 +4648,7 @@
       <c r="H74">
         <v>478052.91</v>
       </c>
-      <c r="I74" s="2" t="s">
+      <c r="I74" s="1" t="s">
         <v>530</v>
       </c>
       <c r="J74" t="s">
@@ -4706,7 +4680,7 @@
       <c r="H75">
         <v>100309.86</v>
       </c>
-      <c r="I75" s="2" t="s">
+      <c r="I75" s="1" t="s">
         <v>531</v>
       </c>
       <c r="J75" t="s">
@@ -4738,7 +4712,7 @@
       <c r="H76">
         <v>477642.73</v>
       </c>
-      <c r="I76" s="2" t="s">
+      <c r="I76" s="1" t="s">
         <v>532</v>
       </c>
       <c r="J76" t="s">
@@ -4770,7 +4744,7 @@
       <c r="H77">
         <v>527611.67</v>
       </c>
-      <c r="I77" s="2" t="s">
+      <c r="I77" s="1" t="s">
         <v>533</v>
       </c>
       <c r="J77" t="s">
@@ -4802,7 +4776,7 @@
       <c r="H78">
         <v>167386.06</v>
       </c>
-      <c r="I78" s="2" t="s">
+      <c r="I78" s="1" t="s">
         <v>534</v>
       </c>
       <c r="J78" t="s">
@@ -4834,7 +4808,7 @@
       <c r="H79">
         <v>216163.54</v>
       </c>
-      <c r="I79" s="2" t="s">
+      <c r="I79" s="1" t="s">
         <v>535</v>
       </c>
       <c r="J79" t="s">
@@ -4866,7 +4840,7 @@
       <c r="H80">
         <v>256360.87</v>
       </c>
-      <c r="I80" s="2" t="s">
+      <c r="I80" s="1" t="s">
         <v>536</v>
       </c>
       <c r="J80" t="s">
@@ -4898,7 +4872,7 @@
       <c r="H81">
         <v>498821.61</v>
       </c>
-      <c r="I81" s="2" t="s">
+      <c r="I81" s="1" t="s">
         <v>537</v>
       </c>
       <c r="J81" t="s">
@@ -4930,7 +4904,7 @@
       <c r="H82">
         <v>432419.35</v>
       </c>
-      <c r="I82" s="2" t="s">
+      <c r="I82" s="1" t="s">
         <v>538</v>
       </c>
       <c r="J82" t="s">
@@ -4962,7 +4936,7 @@
       <c r="H83">
         <v>746941.21</v>
       </c>
-      <c r="I83" s="2" t="s">
+      <c r="I83" s="1" t="s">
         <v>539</v>
       </c>
       <c r="J83" t="s">
@@ -4994,7 +4968,7 @@
       <c r="H84">
         <v>231564.98</v>
       </c>
-      <c r="I84" s="2" t="s">
+      <c r="I84" s="1" t="s">
         <v>540</v>
       </c>
       <c r="J84" t="s">
@@ -5026,7 +5000,7 @@
       <c r="H85">
         <v>787163.38</v>
       </c>
-      <c r="I85" s="2" t="s">
+      <c r="I85" s="1" t="s">
         <v>541</v>
       </c>
       <c r="J85" t="s">
@@ -5058,7 +5032,7 @@
       <c r="H86">
         <v>654597.79</v>
       </c>
-      <c r="I86" s="2" t="s">
+      <c r="I86" s="1" t="s">
         <v>542</v>
       </c>
       <c r="J86" t="s">
@@ -5090,7 +5064,7 @@
       <c r="H87">
         <v>215250.41</v>
       </c>
-      <c r="I87" s="2" t="s">
+      <c r="I87" s="1" t="s">
         <v>543</v>
       </c>
       <c r="J87" t="s">
@@ -5122,7 +5096,7 @@
       <c r="H88">
         <v>228996.24</v>
       </c>
-      <c r="I88" s="2" t="s">
+      <c r="I88" s="1" t="s">
         <v>544</v>
       </c>
       <c r="J88" t="s">
@@ -5154,7 +5128,7 @@
       <c r="H89">
         <v>551560.22</v>
       </c>
-      <c r="I89" s="2" t="s">
+      <c r="I89" s="1" t="s">
         <v>545</v>
       </c>
       <c r="J89" t="s">
@@ -5186,7 +5160,7 @@
       <c r="H90">
         <v>724742.51</v>
       </c>
-      <c r="I90" s="2" t="s">
+      <c r="I90" s="1" t="s">
         <v>546</v>
       </c>
       <c r="J90" t="s">
@@ -5218,7 +5192,7 @@
       <c r="H91">
         <v>341742.74</v>
       </c>
-      <c r="I91" s="2" t="s">
+      <c r="I91" s="1" t="s">
         <v>547</v>
       </c>
       <c r="J91" t="s">
@@ -5250,7 +5224,7 @@
       <c r="H92">
         <v>270177.45</v>
       </c>
-      <c r="I92" s="2" t="s">
+      <c r="I92" s="1" t="s">
         <v>548</v>
       </c>
       <c r="J92" t="s">
@@ -5282,7 +5256,7 @@
       <c r="H93">
         <v>594278.5699999999</v>
       </c>
-      <c r="I93" s="2" t="s">
+      <c r="I93" s="1" t="s">
         <v>549</v>
       </c>
       <c r="J93" t="s">
